--- a/Data/Building/MeetingRoomTwo.Noise.xlsx
+++ b/Data/Building/MeetingRoomTwo.Noise.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H289"/>
+  <dimension ref="A1:I307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709260050</v>
+        <v>1711852324</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -501,6 +506,7 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -519,7 +525,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709260081</v>
+        <v>1711852372</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,6 +539,7 @@
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -551,7 +558,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709260821</v>
+        <v>1711852417</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -565,6 +572,11 @@
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -583,7 +595,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709260888</v>
+        <v>1711852972</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -597,6 +609,7 @@
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,7 +628,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709260894</v>
+        <v>1711853000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -625,10 +638,11 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +661,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709260946</v>
+        <v>1711853022</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -661,6 +675,7 @@
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -679,7 +694,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709260953</v>
+        <v>1711853051</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -693,6 +708,7 @@
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -711,7 +727,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709260990</v>
+        <v>1711853055</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -721,10 +737,11 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -743,7 +760,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709272734</v>
+        <v>1711853089</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -757,6 +774,7 @@
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -775,7 +793,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709272780</v>
+        <v>1711853123</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -789,6 +807,7 @@
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -807,7 +826,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709272828</v>
+        <v>1711853160</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -821,6 +840,11 @@
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -839,7 +863,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709274076</v>
+        <v>1711854332</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -853,6 +877,7 @@
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -871,7 +896,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709274102</v>
+        <v>1711854365</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -885,6 +910,7 @@
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -903,7 +929,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709274106</v>
+        <v>1711854378</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -917,6 +943,7 @@
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -935,7 +962,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709252095</v>
+        <v>1711864656</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -949,6 +976,7 @@
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -967,7 +995,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709252112</v>
+        <v>1711864691</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -981,6 +1009,7 @@
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -999,7 +1028,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709252151</v>
+        <v>1711864764</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1013,6 +1042,11 @@
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1031,7 +1065,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709253311</v>
+        <v>1711866362</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1045,6 +1079,7 @@
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1063,7 +1098,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709253323</v>
+        <v>1711866403</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1073,10 +1108,11 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1095,7 +1131,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709253328</v>
+        <v>1711866425</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1105,10 +1141,11 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1127,7 +1164,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709253350</v>
+        <v>1711867018</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1141,6 +1178,7 @@
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1159,7 +1197,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709253358</v>
+        <v>1711867050</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1173,6 +1211,7 @@
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1191,7 +1230,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709253369</v>
+        <v>1711868771</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1205,6 +1244,7 @@
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1223,7 +1263,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709254825</v>
+        <v>1711868813</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1237,6 +1277,7 @@
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1255,7 +1296,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709265281</v>
+        <v>1711931509</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1269,6 +1310,7 @@
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1287,7 +1329,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709265318</v>
+        <v>1711931542</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1301,6 +1343,7 @@
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1319,7 +1362,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709266040</v>
+        <v>1711931554</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1329,10 +1372,15 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1351,7 +1399,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709266082</v>
+        <v>1711932049</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1361,10 +1409,11 @@
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1383,7 +1432,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709266534</v>
+        <v>1711932060</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1397,6 +1446,7 @@
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1415,7 +1465,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709266579</v>
+        <v>1711932083</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1425,10 +1475,11 @@
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1447,7 +1498,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709267583</v>
+        <v>1711941964</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1461,6 +1512,7 @@
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1479,7 +1531,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709267609</v>
+        <v>1711941993</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1489,10 +1541,11 @@
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1511,7 +1564,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709339340</v>
+        <v>1711942806</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1521,10 +1574,15 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1543,7 +1601,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709339371</v>
+        <v>1711943607</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1557,6 +1615,7 @@
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1575,7 +1634,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709339438</v>
+        <v>1711943626</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1585,10 +1644,11 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1607,7 +1667,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709341116</v>
+        <v>1711943672</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1617,10 +1677,11 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1639,7 +1700,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709341142</v>
+        <v>1712018856</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1653,6 +1714,7 @@
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1671,7 +1733,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709341163</v>
+        <v>1712018878</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1681,10 +1743,11 @@
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1703,7 +1766,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709353097</v>
+        <v>1712019408</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1713,10 +1776,15 @@
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1735,7 +1803,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709353143</v>
+        <v>1712019693</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1749,6 +1817,7 @@
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1767,7 +1836,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709353976</v>
+        <v>1712019713</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1777,10 +1846,11 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1799,7 +1869,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709354289</v>
+        <v>1712019743</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1809,10 +1879,11 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1831,7 +1902,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709354305</v>
+        <v>1712031577</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1845,6 +1916,7 @@
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,7 +1935,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709354333</v>
+        <v>1712031614</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1873,10 +1945,11 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1895,7 +1968,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709425833</v>
+        <v>1712032830</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1905,10 +1978,15 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1927,7 +2005,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709425863</v>
+        <v>1712033037</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1941,6 +2019,7 @@
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1959,7 +2038,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709426087</v>
+        <v>1712033073</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1969,10 +2048,11 @@
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1991,7 +2071,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709427223</v>
+        <v>1712033743</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2001,10 +2081,11 @@
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2023,7 +2104,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709427251</v>
+        <v>1712105414</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2037,6 +2118,7 @@
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2055,7 +2137,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709427259</v>
+        <v>1712105452</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2065,10 +2147,11 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2087,7 +2170,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709438492</v>
+        <v>1712105528</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2097,10 +2180,15 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2119,7 +2207,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709438533</v>
+        <v>1712106531</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2133,6 +2221,7 @@
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2151,7 +2240,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709439533</v>
+        <v>1712106575</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2165,6 +2254,7 @@
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2183,7 +2273,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709439572</v>
+        <v>1712106602</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2197,6 +2287,7 @@
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2215,7 +2306,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709440786</v>
+        <v>1712119355</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2229,6 +2320,7 @@
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2247,7 +2339,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709440809</v>
+        <v>1712119366</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2261,6 +2353,7 @@
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2279,7 +2372,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709441651</v>
+        <v>1712119413</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2289,10 +2382,15 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2311,7 +2409,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709441700</v>
+        <v>1712120324</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2321,10 +2419,11 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2343,7 +2442,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709512232</v>
+        <v>1712120352</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2357,6 +2456,7 @@
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2375,7 +2475,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709512265</v>
+        <v>1712120388</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2385,10 +2485,11 @@
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2407,7 +2508,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709512316</v>
+        <v>1712120445</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2417,10 +2518,11 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2439,7 +2541,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709513082</v>
+        <v>1712120484</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2453,6 +2555,7 @@
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2471,7 +2574,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709513090</v>
+        <v>1712120530</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2481,10 +2584,15 @@
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,7 +2611,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709513103</v>
+        <v>1712121733</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2513,10 +2621,11 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2535,7 +2644,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709513310</v>
+        <v>1712121749</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2549,6 +2658,7 @@
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2567,7 +2677,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709513350</v>
+        <v>1712121765</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2577,10 +2687,11 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2599,7 +2710,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709513393</v>
+        <v>1712189085</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2609,10 +2720,11 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2631,7 +2743,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709514409</v>
+        <v>1712189140</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2645,6 +2757,7 @@
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2663,7 +2776,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709514440</v>
+        <v>1712189200</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2673,10 +2786,15 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2695,7 +2813,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709514447</v>
+        <v>1712190066</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2705,10 +2823,11 @@
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2727,7 +2846,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709524142</v>
+        <v>1712190090</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2741,6 +2860,7 @@
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2759,7 +2879,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709524183</v>
+        <v>1712190104</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2769,10 +2889,11 @@
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2791,7 +2912,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709525637</v>
+        <v>1712204696</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2805,6 +2926,7 @@
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2823,7 +2945,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709525660</v>
+        <v>1712204724</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2833,10 +2955,11 @@
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2855,7 +2978,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709526679</v>
+        <v>1712204780</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2865,10 +2988,15 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2887,7 +3015,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709526711</v>
+        <v>1712206008</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -2901,6 +3029,7 @@
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2919,7 +3048,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709526767</v>
+        <v>1712206043</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2929,10 +3058,11 @@
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2951,7 +3081,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709528213</v>
+        <v>1712206055</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2961,10 +3091,11 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2983,7 +3114,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709528221</v>
+        <v>1712275957</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -2997,6 +3128,7 @@
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3015,7 +3147,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709528239</v>
+        <v>1712275992</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3025,10 +3157,11 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3047,7 +3180,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709599362</v>
+        <v>1712276087</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3057,10 +3190,15 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3079,7 +3217,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709599396</v>
+        <v>1712277808</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3093,6 +3231,7 @@
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3111,7 +3250,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709599417</v>
+        <v>1712277838</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3121,10 +3260,11 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3143,7 +3283,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709600781</v>
+        <v>1712277861</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3153,10 +3293,11 @@
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3175,7 +3316,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1709600812</v>
+        <v>1712289001</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3189,6 +3330,7 @@
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3207,7 +3349,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1709600823</v>
+        <v>1712289042</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3217,10 +3359,11 @@
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3239,7 +3382,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1709614227</v>
+        <v>1712290778</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3249,10 +3392,15 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3271,7 +3419,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1709614265</v>
+        <v>1712290941</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3285,6 +3433,7 @@
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3303,7 +3452,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1709615117</v>
+        <v>1712290958</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3313,10 +3462,11 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3335,7 +3485,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1709615402</v>
+        <v>1712290962</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3345,10 +3495,11 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3367,7 +3518,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1709615436</v>
+        <v>1712538127</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3381,6 +3532,7 @@
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3399,7 +3551,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1709615437</v>
+        <v>1712538158</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3409,10 +3561,11 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3431,7 +3584,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1709855656</v>
+        <v>1712538219</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3441,10 +3594,15 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3463,7 +3621,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1709855673</v>
+        <v>1712539394</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3477,6 +3635,7 @@
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3495,7 +3654,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1709855738</v>
+        <v>1712539434</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3505,10 +3664,11 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3527,7 +3687,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1709856989</v>
+        <v>1712539444</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3537,10 +3697,11 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3559,7 +3720,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1709857027</v>
+        <v>1712548335</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3573,6 +3734,7 @@
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3591,7 +3753,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1709857074</v>
+        <v>1712548363</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3601,10 +3763,11 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3623,7 +3786,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1709867490</v>
+        <v>1712548411</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -3633,10 +3796,15 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3655,7 +3823,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1709867522</v>
+        <v>1712549119</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -3669,6 +3837,7 @@
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3687,7 +3856,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1709867583</v>
+        <v>1712549152</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -3697,10 +3866,11 @@
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3719,7 +3889,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1709868984</v>
+        <v>1712549195</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -3729,10 +3899,11 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3751,7 +3922,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1709869009</v>
+        <v>1712550656</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -3765,6 +3936,7 @@
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3783,7 +3955,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1709869017</v>
+        <v>1712550673</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -3793,10 +3965,11 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3815,7 +3988,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1709944832</v>
+        <v>1712551371</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -3829,6 +4002,7 @@
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3847,7 +4021,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1709944860</v>
+        <v>1712551409</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -3857,10 +4031,11 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3879,7 +4054,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1709944936</v>
+        <v>1712624398</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3889,10 +4064,11 @@
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3911,7 +4087,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1709945999</v>
+        <v>1712624436</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3925,6 +4101,7 @@
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3943,7 +4120,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1709946043</v>
+        <v>1712624469</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -3953,10 +4130,15 @@
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3975,7 +4157,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1709946048</v>
+        <v>1712624892</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3985,10 +4167,11 @@
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4007,7 +4190,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1709955152</v>
+        <v>1712624912</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4021,6 +4204,7 @@
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4039,7 +4223,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1709955177</v>
+        <v>1712624926</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4049,10 +4233,11 @@
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4071,7 +4256,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1709955234</v>
+        <v>1712636647</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4081,10 +4266,11 @@
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4103,7 +4289,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1709956832</v>
+        <v>1712636662</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4117,6 +4303,7 @@
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4135,7 +4322,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1709956858</v>
+        <v>1712636669</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4145,10 +4332,15 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4167,7 +4359,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1709956861</v>
+        <v>1712637533</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4177,10 +4369,11 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4199,7 +4392,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710032452</v>
+        <v>1712637551</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4213,6 +4406,7 @@
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4231,7 +4425,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710032496</v>
+        <v>1712637553</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4241,10 +4435,11 @@
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4263,7 +4458,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710032503</v>
+        <v>1712710864</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4273,10 +4468,11 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4295,7 +4491,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710033397</v>
+        <v>1712710887</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4309,6 +4505,7 @@
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4327,7 +4524,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710033423</v>
+        <v>1712711590</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4341,6 +4538,7 @@
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4359,7 +4557,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710033451</v>
+        <v>1712711623</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4373,6 +4571,7 @@
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4391,7 +4590,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710043401</v>
+        <v>1712712290</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4405,6 +4604,7 @@
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4423,7 +4623,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710043437</v>
+        <v>1712712321</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4437,6 +4637,7 @@
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4455,7 +4656,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710043493</v>
+        <v>1712714108</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4465,10 +4666,11 @@
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4487,7 +4689,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710045656</v>
+        <v>1712714145</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -4497,10 +4699,11 @@
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4519,7 +4722,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710045687</v>
+        <v>1712722613</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -4533,6 +4736,7 @@
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4551,7 +4755,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710045690</v>
+        <v>1712722640</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4561,10 +4765,11 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -4583,7 +4788,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710047007</v>
+        <v>1712722720</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4593,10 +4798,15 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -4615,7 +4825,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710047059</v>
+        <v>1712723951</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -4629,6 +4839,7 @@
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4647,7 +4858,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710048927</v>
+        <v>1712723958</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -4661,6 +4872,7 @@
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4679,7 +4891,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710048962</v>
+        <v>1712723972</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -4693,6 +4905,7 @@
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4711,7 +4924,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710117873</v>
+        <v>1712724154</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -4725,6 +4938,7 @@
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4743,7 +4957,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710117907</v>
+        <v>1712724188</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -4757,6 +4971,7 @@
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4775,7 +4990,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710117970</v>
+        <v>1712725642</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -4785,10 +5000,11 @@
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4807,7 +5023,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710119578</v>
+        <v>1712725689</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -4817,10 +5033,11 @@
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4839,7 +5056,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710119607</v>
+        <v>1712798421</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -4853,6 +5070,7 @@
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4871,7 +5089,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710119622</v>
+        <v>1712798453</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4881,10 +5099,11 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4903,7 +5122,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710132417</v>
+        <v>1712798500</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4913,10 +5132,15 @@
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4935,7 +5159,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710132424</v>
+        <v>1712799258</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4949,6 +5173,7 @@
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4967,7 +5192,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710132443</v>
+        <v>1712799273</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4977,10 +5202,11 @@
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4999,7 +5225,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710133809</v>
+        <v>1712799310</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5009,10 +5235,11 @@
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5031,7 +5258,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710133844</v>
+        <v>1712808019</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5045,6 +5272,7 @@
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5063,7 +5291,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710134001</v>
+        <v>1712808056</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5073,10 +5301,11 @@
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5095,7 +5324,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710204286</v>
+        <v>1712808102</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5105,10 +5334,15 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5127,7 +5361,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710204314</v>
+        <v>1712808743</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5141,6 +5375,7 @@
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5159,7 +5394,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710204727</v>
+        <v>1712808757</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5169,10 +5404,11 @@
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5191,7 +5427,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710205528</v>
+        <v>1712808797</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5201,10 +5437,11 @@
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5223,7 +5460,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710205561</v>
+        <v>1712809341</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5237,6 +5474,7 @@
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5255,7 +5493,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710205694</v>
+        <v>1712809375</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5265,10 +5503,11 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5287,7 +5526,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710217923</v>
+        <v>1712809423</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5297,10 +5536,15 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5319,7 +5563,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710217958</v>
+        <v>1712810603</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5333,6 +5577,7 @@
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5351,7 +5596,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710219064</v>
+        <v>1712810638</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5361,10 +5606,11 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5383,7 +5629,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710219432</v>
+        <v>1712810661</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -5393,10 +5639,11 @@
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -5415,7 +5662,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710219464</v>
+        <v>1712883575</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -5429,6 +5676,7 @@
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -5447,7 +5695,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710220542</v>
+        <v>1712883605</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -5457,10 +5705,11 @@
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -5479,7 +5728,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710463360</v>
+        <v>1712883650</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -5489,10 +5738,15 @@
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -5511,7 +5765,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710463391</v>
+        <v>1712885485</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -5525,6 +5779,7 @@
         </is>
       </c>
       <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -5543,7 +5798,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710463417</v>
+        <v>1712885522</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -5553,10 +5808,11 @@
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -5575,7 +5831,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710464651</v>
+        <v>1712885623</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -5585,10 +5841,11 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -5607,7 +5864,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710464667</v>
+        <v>1712896027</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -5621,6 +5878,7 @@
         </is>
       </c>
       <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -5639,7 +5897,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710464674</v>
+        <v>1712896080</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -5649,10 +5907,11 @@
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -5671,7 +5930,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1710474950</v>
+        <v>1712896097</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -5681,10 +5940,15 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -5703,7 +5967,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1710474987</v>
+        <v>1712897613</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -5717,6 +5981,7 @@
         </is>
       </c>
       <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -5735,7 +6000,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1710475431</v>
+        <v>1712897642</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -5745,10 +6010,11 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -5767,7 +6033,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1710475469</v>
+        <v>1712897642</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -5777,10 +6043,11 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -5799,7 +6066,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1710475483</v>
+        <v>1713140644</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -5813,6 +6080,7 @@
         </is>
       </c>
       <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -5831,7 +6099,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1710475832</v>
+        <v>1713140677</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -5841,10 +6109,11 @@
       <c r="F169" t="inlineStr"/>
       <c r="G169" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -5863,7 +6132,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1710548405</v>
+        <v>1713140748</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -5873,10 +6142,15 @@
       <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5895,7 +6169,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1710548443</v>
+        <v>1713141517</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -5909,6 +6183,7 @@
         </is>
       </c>
       <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5927,7 +6202,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1710548788</v>
+        <v>1713141544</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -5937,10 +6212,11 @@
       <c r="F172" t="inlineStr"/>
       <c r="G172" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5959,7 +6235,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1710549435</v>
+        <v>1713141547</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -5969,10 +6245,11 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5991,7 +6268,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1710549467</v>
+        <v>1713152262</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6005,6 +6282,7 @@
         </is>
       </c>
       <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6023,7 +6301,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1710549472</v>
+        <v>1713152288</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6033,10 +6311,11 @@
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6055,7 +6334,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1710562913</v>
+        <v>1713153017</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6065,10 +6344,15 @@
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6087,7 +6371,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1710562937</v>
+        <v>1713153694</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6101,6 +6385,7 @@
         </is>
       </c>
       <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6119,7 +6404,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1710562968</v>
+        <v>1713153713</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6129,10 +6414,11 @@
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6151,7 +6437,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1710564371</v>
+        <v>1713153725</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6161,10 +6447,11 @@
       <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6183,7 +6470,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1710564412</v>
+        <v>1713226227</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6197,6 +6484,7 @@
         </is>
       </c>
       <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6215,7 +6503,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1710564418</v>
+        <v>1713226259</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6225,10 +6513,11 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6247,7 +6536,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1710637191</v>
+        <v>1713227263</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6257,10 +6546,15 @@
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -6279,7 +6573,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1710637230</v>
+        <v>1713227582</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -6293,6 +6587,7 @@
         </is>
       </c>
       <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -6311,7 +6606,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1710637279</v>
+        <v>1713227648</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -6321,10 +6616,11 @@
       <c r="F184" t="inlineStr"/>
       <c r="G184" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6343,7 +6639,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1710638668</v>
+        <v>1713227844</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -6353,10 +6649,11 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -6375,7 +6672,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1710638685</v>
+        <v>1713238095</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -6389,6 +6686,7 @@
         </is>
       </c>
       <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -6407,7 +6705,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1710638714</v>
+        <v>1713238150</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -6417,10 +6715,11 @@
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -6439,7 +6738,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1710650414</v>
+        <v>1713238193</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -6449,10 +6748,15 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -6471,7 +6775,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1710650447</v>
+        <v>1713238827</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -6485,6 +6789,7 @@
         </is>
       </c>
       <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -6503,7 +6808,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1710650492</v>
+        <v>1713238846</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -6513,10 +6818,11 @@
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -6535,7 +6841,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1710651384</v>
+        <v>1713238864</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -6545,10 +6851,11 @@
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -6567,7 +6874,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1710651403</v>
+        <v>1713314142</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -6581,6 +6888,7 @@
         </is>
       </c>
       <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -6599,7 +6907,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1710651429</v>
+        <v>1713314231</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -6609,10 +6917,11 @@
       <c r="F193" t="inlineStr"/>
       <c r="G193" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -6631,7 +6940,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1710722257</v>
+        <v>1713314311</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -6641,10 +6950,15 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -6663,7 +6977,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1710722287</v>
+        <v>1713315184</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -6677,6 +6991,7 @@
         </is>
       </c>
       <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -6695,7 +7010,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1710722321</v>
+        <v>1713315212</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -6705,10 +7020,11 @@
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -6727,7 +7043,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1710723783</v>
+        <v>1713315216</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -6737,10 +7053,11 @@
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -6759,7 +7076,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1710723811</v>
+        <v>1713325054</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -6773,6 +7090,7 @@
         </is>
       </c>
       <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -6791,7 +7109,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1710723829</v>
+        <v>1713325091</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -6801,10 +7119,11 @@
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -6823,7 +7142,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1710734828</v>
+        <v>1713325514</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -6837,6 +7156,7 @@
         </is>
       </c>
       <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -6855,7 +7175,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1710734862</v>
+        <v>1713325550</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -6865,10 +7185,11 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -6887,7 +7208,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1710734925</v>
+        <v>1713326083</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -6897,10 +7218,11 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -6919,7 +7241,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1710736399</v>
+        <v>1713326113</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -6933,6 +7255,7 @@
         </is>
       </c>
       <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -6951,7 +7274,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1710736428</v>
+        <v>1713326165</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -6961,10 +7284,15 @@
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -6983,7 +7311,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1710736449</v>
+        <v>1713326889</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -6993,10 +7321,11 @@
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7015,7 +7344,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1710808581</v>
+        <v>1713326943</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7029,6 +7358,7 @@
         </is>
       </c>
       <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7047,7 +7377,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1710808611</v>
+        <v>1713326952</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7057,10 +7387,11 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7079,7 +7410,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1710808683</v>
+        <v>1713398035</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7089,10 +7420,11 @@
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7111,7 +7443,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1710810375</v>
+        <v>1713398067</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7125,6 +7457,7 @@
         </is>
       </c>
       <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7143,7 +7476,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1710810401</v>
+        <v>1713398121</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7153,10 +7486,15 @@
       <c r="F210" t="inlineStr"/>
       <c r="G210" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -7175,7 +7513,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1710810409</v>
+        <v>1713398698</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -7185,10 +7523,11 @@
       <c r="F211" t="inlineStr"/>
       <c r="G211" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -7207,7 +7546,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1710821935</v>
+        <v>1713398734</v>
       </c>
       <c r="E212" t="inlineStr">
         <is>
@@ -7221,6 +7560,7 @@
         </is>
       </c>
       <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -7239,7 +7579,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1710821977</v>
+        <v>1713398759</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
@@ -7249,10 +7589,11 @@
       <c r="F213" t="inlineStr"/>
       <c r="G213" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -7271,7 +7612,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1710822331</v>
+        <v>1713409262</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
@@ -7281,10 +7622,11 @@
       <c r="F214" t="inlineStr"/>
       <c r="G214" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7303,7 +7645,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1710822681</v>
+        <v>1713409292</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
@@ -7317,6 +7659,7 @@
         </is>
       </c>
       <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -7335,7 +7678,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1710822709</v>
+        <v>1713409823</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
@@ -7349,6 +7692,7 @@
         </is>
       </c>
       <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -7367,7 +7711,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1710823278</v>
+        <v>1713409857</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
@@ -7381,6 +7725,7 @@
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -7399,7 +7744,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1711067366</v>
+        <v>1713410023</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
@@ -7413,6 +7758,7 @@
         </is>
       </c>
       <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -7431,7 +7777,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1711067397</v>
+        <v>1713410064</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
@@ -7445,6 +7791,7 @@
         </is>
       </c>
       <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -7463,7 +7810,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1711067442</v>
+        <v>1713410984</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
@@ -7473,10 +7820,11 @@
       <c r="F220" t="inlineStr"/>
       <c r="G220" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -7495,7 +7843,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1711068166</v>
+        <v>1713411009</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
@@ -7505,10 +7853,11 @@
       <c r="F221" t="inlineStr"/>
       <c r="G221" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -7527,7 +7876,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1711068201</v>
+        <v>1713487219</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
@@ -7541,6 +7890,7 @@
         </is>
       </c>
       <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -7559,7 +7909,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1711068207</v>
+        <v>1713487266</v>
       </c>
       <c r="E223" t="inlineStr">
         <is>
@@ -7569,10 +7919,11 @@
       <c r="F223" t="inlineStr"/>
       <c r="G223" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -7591,7 +7942,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1711080526</v>
+        <v>1713487327</v>
       </c>
       <c r="E224" t="inlineStr">
         <is>
@@ -7601,10 +7952,15 @@
       <c r="F224" t="inlineStr"/>
       <c r="G224" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -7623,7 +7979,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1711080559</v>
+        <v>1713487940</v>
       </c>
       <c r="E225" t="inlineStr">
         <is>
@@ -7637,6 +7993,7 @@
         </is>
       </c>
       <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -7655,7 +8012,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1711080606</v>
+        <v>1713487976</v>
       </c>
       <c r="E226" t="inlineStr">
         <is>
@@ -7665,10 +8022,11 @@
       <c r="F226" t="inlineStr"/>
       <c r="G226" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -7687,7 +8045,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1711081033</v>
+        <v>1713488052</v>
       </c>
       <c r="E227" t="inlineStr">
         <is>
@@ -7697,10 +8055,11 @@
       <c r="F227" t="inlineStr"/>
       <c r="G227" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -7719,7 +8078,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1711081066</v>
+        <v>1713498507</v>
       </c>
       <c r="E228" t="inlineStr">
         <is>
@@ -7733,6 +8092,7 @@
         </is>
       </c>
       <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -7751,7 +8111,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1711081076</v>
+        <v>1713498524</v>
       </c>
       <c r="E229" t="inlineStr">
         <is>
@@ -7761,10 +8121,11 @@
       <c r="F229" t="inlineStr"/>
       <c r="G229" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -7783,7 +8144,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1711081486</v>
+        <v>1713498569</v>
       </c>
       <c r="E230" t="inlineStr">
         <is>
@@ -7793,10 +8154,15 @@
       <c r="F230" t="inlineStr"/>
       <c r="G230" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -7815,7 +8181,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1711081525</v>
+        <v>1713499598</v>
       </c>
       <c r="E231" t="inlineStr">
         <is>
@@ -7829,6 +8195,7 @@
         </is>
       </c>
       <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -7847,7 +8214,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1711081571</v>
+        <v>1713499614</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
@@ -7857,10 +8224,11 @@
       <c r="F232" t="inlineStr"/>
       <c r="G232" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -7879,7 +8247,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1711082509</v>
+        <v>1713499641</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
@@ -7889,10 +8257,11 @@
       <c r="F233" t="inlineStr"/>
       <c r="G233" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -7911,7 +8280,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1711082536</v>
+        <v>1713744622</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
@@ -7925,6 +8294,7 @@
         </is>
       </c>
       <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -7943,7 +8313,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1711082539</v>
+        <v>1713744652</v>
       </c>
       <c r="E235" t="inlineStr">
         <is>
@@ -7953,10 +8323,11 @@
       <c r="F235" t="inlineStr"/>
       <c r="G235" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -7975,7 +8346,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1711153727</v>
+        <v>1713744709</v>
       </c>
       <c r="E236" t="inlineStr">
         <is>
@@ -7985,10 +8356,15 @@
       <c r="F236" t="inlineStr"/>
       <c r="G236" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -8007,7 +8383,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1711153765</v>
+        <v>1713745871</v>
       </c>
       <c r="E237" t="inlineStr">
         <is>
@@ -8021,6 +8397,7 @@
         </is>
       </c>
       <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -8039,7 +8416,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1711153930</v>
+        <v>1713745901</v>
       </c>
       <c r="E238" t="inlineStr">
         <is>
@@ -8049,10 +8426,11 @@
       <c r="F238" t="inlineStr"/>
       <c r="G238" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -8071,7 +8449,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1711154912</v>
+        <v>1713745914</v>
       </c>
       <c r="E239" t="inlineStr">
         <is>
@@ -8081,10 +8459,11 @@
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -8103,7 +8482,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1711154924</v>
+        <v>1713754592</v>
       </c>
       <c r="E240" t="inlineStr">
         <is>
@@ -8117,6 +8496,7 @@
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -8135,7 +8515,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1711154937</v>
+        <v>1713754619</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
@@ -8145,10 +8525,11 @@
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -8167,7 +8548,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1711167532</v>
+        <v>1713754686</v>
       </c>
       <c r="E242" t="inlineStr">
         <is>
@@ -8177,10 +8558,15 @@
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -8199,7 +8585,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1711167558</v>
+        <v>1713755447</v>
       </c>
       <c r="E243" t="inlineStr">
         <is>
@@ -8213,6 +8599,7 @@
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -8231,7 +8618,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1711167615</v>
+        <v>1713755472</v>
       </c>
       <c r="E244" t="inlineStr">
         <is>
@@ -8241,10 +8628,11 @@
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -8263,7 +8651,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1711168550</v>
+        <v>1713755491</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
@@ -8277,6 +8665,7 @@
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -8295,7 +8684,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1711168577</v>
+        <v>1713755500</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
@@ -8309,6 +8698,7 @@
         </is>
       </c>
       <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -8327,7 +8717,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1711169962</v>
+        <v>1713755505</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
@@ -8341,6 +8731,7 @@
         </is>
       </c>
       <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -8359,7 +8750,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1711239489</v>
+        <v>1713755576</v>
       </c>
       <c r="E248" t="inlineStr">
         <is>
@@ -8373,6 +8764,7 @@
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -8391,7 +8783,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1711239521</v>
+        <v>1713755638</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
@@ -8405,6 +8797,7 @@
         </is>
       </c>
       <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -8423,7 +8816,7 @@
         </is>
       </c>
       <c r="D250" t="n">
-        <v>1711239577</v>
+        <v>1713755701</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
@@ -8433,10 +8826,11 @@
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -8455,7 +8849,7 @@
         </is>
       </c>
       <c r="D251" t="n">
-        <v>1711240700</v>
+        <v>1713755738</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
@@ -8465,10 +8859,11 @@
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -8487,7 +8882,7 @@
         </is>
       </c>
       <c r="D252" t="n">
-        <v>1711240736</v>
+        <v>1713832660</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
@@ -8501,6 +8896,7 @@
         </is>
       </c>
       <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -8519,7 +8915,7 @@
         </is>
       </c>
       <c r="D253" t="n">
-        <v>1711240743</v>
+        <v>1713832700</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
@@ -8529,10 +8925,11 @@
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -8551,7 +8948,7 @@
         </is>
       </c>
       <c r="D254" t="n">
-        <v>1711240856</v>
+        <v>1713832777</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
@@ -8561,10 +8958,15 @@
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -8583,7 +8985,7 @@
         </is>
       </c>
       <c r="D255" t="n">
-        <v>1711240892</v>
+        <v>1713834364</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
@@ -8597,6 +8999,7 @@
         </is>
       </c>
       <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -8615,7 +9018,7 @@
         </is>
       </c>
       <c r="D256" t="n">
-        <v>1711240940</v>
+        <v>1713834397</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
@@ -8625,10 +9028,11 @@
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -8647,7 +9051,7 @@
         </is>
       </c>
       <c r="D257" t="n">
-        <v>1711241922</v>
+        <v>1713834403</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
@@ -8657,10 +9061,11 @@
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -8679,7 +9084,7 @@
         </is>
       </c>
       <c r="D258" t="n">
-        <v>1711241949</v>
+        <v>1713846043</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
@@ -8693,6 +9098,7 @@
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -8711,7 +9117,7 @@
         </is>
       </c>
       <c r="D259" t="n">
-        <v>1711241961</v>
+        <v>1713846067</v>
       </c>
       <c r="E259" t="inlineStr">
         <is>
@@ -8721,10 +9127,11 @@
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -8743,7 +9150,7 @@
         </is>
       </c>
       <c r="D260" t="n">
-        <v>1711251556</v>
+        <v>1713846645</v>
       </c>
       <c r="E260" t="inlineStr">
         <is>
@@ -8757,6 +9164,7 @@
         </is>
       </c>
       <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -8775,7 +9183,7 @@
         </is>
       </c>
       <c r="D261" t="n">
-        <v>1711251597</v>
+        <v>1713846703</v>
       </c>
       <c r="E261" t="inlineStr">
         <is>
@@ -8785,10 +9193,11 @@
       <c r="F261" t="inlineStr"/>
       <c r="G261" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -8807,7 +9216,7 @@
         </is>
       </c>
       <c r="D262" t="n">
-        <v>1711252818</v>
+        <v>1713847090</v>
       </c>
       <c r="E262" t="inlineStr">
         <is>
@@ -8817,10 +9226,11 @@
       <c r="F262" t="inlineStr"/>
       <c r="G262" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -8839,7 +9249,7 @@
         </is>
       </c>
       <c r="D263" t="n">
-        <v>1711253317</v>
+        <v>1713847123</v>
       </c>
       <c r="E263" t="inlineStr">
         <is>
@@ -8853,6 +9263,7 @@
         </is>
       </c>
       <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -8871,7 +9282,7 @@
         </is>
       </c>
       <c r="D264" t="n">
-        <v>1711253346</v>
+        <v>1713847163</v>
       </c>
       <c r="E264" t="inlineStr">
         <is>
@@ -8881,10 +9292,15 @@
       <c r="F264" t="inlineStr"/>
       <c r="G264" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -8903,7 +9319,7 @@
         </is>
       </c>
       <c r="D265" t="n">
-        <v>1711253353</v>
+        <v>1713847904</v>
       </c>
       <c r="E265" t="inlineStr">
         <is>
@@ -8913,10 +9329,11 @@
       <c r="F265" t="inlineStr"/>
       <c r="G265" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -8935,7 +9352,7 @@
         </is>
       </c>
       <c r="D266" t="n">
-        <v>1711326194</v>
+        <v>1713847930</v>
       </c>
       <c r="E266" t="inlineStr">
         <is>
@@ -8949,6 +9366,7 @@
         </is>
       </c>
       <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -8967,7 +9385,7 @@
         </is>
       </c>
       <c r="D267" t="n">
-        <v>1711326208</v>
+        <v>1713847941</v>
       </c>
       <c r="E267" t="inlineStr">
         <is>
@@ -8977,10 +9395,11 @@
       <c r="F267" t="inlineStr"/>
       <c r="G267" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -8999,7 +9418,7 @@
         </is>
       </c>
       <c r="D268" t="n">
-        <v>1711326254</v>
+        <v>1713918047</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
@@ -9009,10 +9428,11 @@
       <c r="F268" t="inlineStr"/>
       <c r="G268" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -9031,7 +9451,7 @@
         </is>
       </c>
       <c r="D269" t="n">
-        <v>1711326576</v>
+        <v>1713918075</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
@@ -9045,6 +9465,7 @@
         </is>
       </c>
       <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -9063,7 +9484,7 @@
         </is>
       </c>
       <c r="D270" t="n">
-        <v>1711326604</v>
+        <v>1713918134</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
@@ -9073,10 +9494,15 @@
       <c r="F270" t="inlineStr"/>
       <c r="G270" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -9095,7 +9521,7 @@
         </is>
       </c>
       <c r="D271" t="n">
-        <v>1711326605</v>
+        <v>1713918708</v>
       </c>
       <c r="E271" t="inlineStr">
         <is>
@@ -9105,10 +9531,11 @@
       <c r="F271" t="inlineStr"/>
       <c r="G271" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -9127,7 +9554,7 @@
         </is>
       </c>
       <c r="D272" t="n">
-        <v>1711338524</v>
+        <v>1713918737</v>
       </c>
       <c r="E272" t="inlineStr">
         <is>
@@ -9141,6 +9568,7 @@
         </is>
       </c>
       <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -9159,7 +9587,7 @@
         </is>
       </c>
       <c r="D273" t="n">
-        <v>1711338556</v>
+        <v>1713918738</v>
       </c>
       <c r="E273" t="inlineStr">
         <is>
@@ -9169,10 +9597,11 @@
       <c r="F273" t="inlineStr"/>
       <c r="G273" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -9191,7 +9620,7 @@
         </is>
       </c>
       <c r="D274" t="n">
-        <v>1711338621</v>
+        <v>1713931284</v>
       </c>
       <c r="E274" t="inlineStr">
         <is>
@@ -9201,10 +9630,11 @@
       <c r="F274" t="inlineStr"/>
       <c r="G274" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -9223,7 +9653,7 @@
         </is>
       </c>
       <c r="D275" t="n">
-        <v>1711340390</v>
+        <v>1713931318</v>
       </c>
       <c r="E275" t="inlineStr">
         <is>
@@ -9237,6 +9667,7 @@
         </is>
       </c>
       <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -9255,7 +9686,7 @@
         </is>
       </c>
       <c r="D276" t="n">
-        <v>1711340415</v>
+        <v>1713931630</v>
       </c>
       <c r="E276" t="inlineStr">
         <is>
@@ -9265,10 +9696,15 @@
       <c r="F276" t="inlineStr"/>
       <c r="G276" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -9287,7 +9723,7 @@
         </is>
       </c>
       <c r="D277" t="n">
-        <v>1711340424</v>
+        <v>1713932841</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
@@ -9297,10 +9733,11 @@
       <c r="F277" t="inlineStr"/>
       <c r="G277" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -9319,7 +9756,7 @@
         </is>
       </c>
       <c r="D278" t="n">
-        <v>1711414154</v>
+        <v>1713932868</v>
       </c>
       <c r="E278" t="inlineStr">
         <is>
@@ -9333,6 +9770,7 @@
         </is>
       </c>
       <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -9351,7 +9789,7 @@
         </is>
       </c>
       <c r="D279" t="n">
-        <v>1711414189</v>
+        <v>1713932883</v>
       </c>
       <c r="E279" t="inlineStr">
         <is>
@@ -9361,10 +9799,11 @@
       <c r="F279" t="inlineStr"/>
       <c r="G279" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -9383,7 +9822,7 @@
         </is>
       </c>
       <c r="D280" t="n">
-        <v>1711414567</v>
+        <v>1714002405</v>
       </c>
       <c r="E280" t="inlineStr">
         <is>
@@ -9393,10 +9832,11 @@
       <c r="F280" t="inlineStr"/>
       <c r="G280" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -9415,7 +9855,7 @@
         </is>
       </c>
       <c r="D281" t="n">
-        <v>1711415841</v>
+        <v>1714002444</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
@@ -9429,6 +9869,7 @@
         </is>
       </c>
       <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -9447,7 +9888,7 @@
         </is>
       </c>
       <c r="D282" t="n">
-        <v>1711415879</v>
+        <v>1714002523</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
@@ -9457,10 +9898,15 @@
       <c r="F282" t="inlineStr"/>
       <c r="G282" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -9479,7 +9925,7 @@
         </is>
       </c>
       <c r="D283" t="n">
-        <v>1711415885</v>
+        <v>1714003518</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
@@ -9489,10 +9935,11 @@
       <c r="F283" t="inlineStr"/>
       <c r="G283" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
         </is>
       </c>
       <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -9511,7 +9958,7 @@
         </is>
       </c>
       <c r="D284" t="n">
-        <v>1711426573</v>
+        <v>1714003528</v>
       </c>
       <c r="E284" t="inlineStr">
         <is>
@@ -9525,6 +9972,7 @@
         </is>
       </c>
       <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -9543,7 +9991,7 @@
         </is>
       </c>
       <c r="D285" t="n">
-        <v>1711426608</v>
+        <v>1714003556</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
@@ -9553,10 +10001,11 @@
       <c r="F285" t="inlineStr"/>
       <c r="G285" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
       <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -9575,7 +10024,7 @@
         </is>
       </c>
       <c r="D286" t="n">
-        <v>1711426665</v>
+        <v>1714014432</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
@@ -9585,10 +10034,11 @@
       <c r="F286" t="inlineStr"/>
       <c r="G286" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
         </is>
       </c>
       <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -9607,7 +10057,7 @@
         </is>
       </c>
       <c r="D287" t="n">
-        <v>1711427909</v>
+        <v>1714014466</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
@@ -9621,6 +10071,7 @@
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -9639,7 +10090,7 @@
         </is>
       </c>
       <c r="D288" t="n">
-        <v>1711427944</v>
+        <v>1714014511</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
@@ -9649,10 +10100,15 @@
       <c r="F288" t="inlineStr"/>
       <c r="G288" t="inlineStr">
         <is>
-          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
         </is>
       </c>
       <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -9671,7 +10127,7 @@
         </is>
       </c>
       <c r="D289" t="n">
-        <v>1711427947</v>
+        <v>1714015304</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
@@ -9681,10 +10137,613 @@
       <c r="F289" t="inlineStr"/>
       <c r="G289" t="inlineStr">
         <is>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D290" t="n">
+        <v>1714015327</v>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D291" t="n">
+        <v>1714015335</v>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
           <t>MeetingRoomTwo.Noise.state: Quiet</t>
         </is>
       </c>
-      <c r="H289" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D292" t="n">
+        <v>1714089457</v>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D293" t="n">
+        <v>1714089496</v>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D294" t="n">
+        <v>1714089529</v>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D295" t="n">
+        <v>1714089880</v>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr"/>
+      <c r="I295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D296" t="n">
+        <v>1714089904</v>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
+      <c r="I296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D297" t="n">
+        <v>1714089919</v>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr"/>
+      <c r="I297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D298" t="n">
+        <v>1714099690</v>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
+      <c r="I298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D299" t="n">
+        <v>1714099729</v>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr"/>
+      <c r="I299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>1714100349</v>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr"/>
+      <c r="I300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D301" t="n">
+        <v>1714100387</v>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr"/>
+      <c r="I301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D302" t="n">
+        <v>1714101712</v>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr"/>
+      <c r="I302" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D303" t="n">
+        <v>1714101755</v>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr"/>
+      <c r="I303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D304" t="n">
+        <v>1714101804</v>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ExcessivelyNoisy</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr"/>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>#6</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D305" t="n">
+        <v>1714102952</v>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: Noisy</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
+      <c r="I305" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D306" t="n">
+        <v>1714102973</v>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: ComfortableSilence</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr"/>
+      <c r="I306" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Noise_Change</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo</t>
+        </is>
+      </c>
+      <c r="D307" t="n">
+        <v>1714102993</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>INFO</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>MeetingRoomTwo.Noise.state: Quiet</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr"/>
+      <c r="I307" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
